--- a/public/file/template_input.xlsx
+++ b/public/file/template_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FAHD\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C2AE99-70F8-44A1-A8DC-C10C6ED6B1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0324EB97-8DC5-432A-A08E-0E82C4993801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FF9404A3-B408-4DC3-B687-F8E2C50F4E09}"/>
   </bookViews>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>DESKRIPSI</t>
   </si>
@@ -33,9 +44,6 @@
     <t>SATUAN</t>
   </si>
   <si>
-    <t>HARGA</t>
-  </si>
-  <si>
     <t>KATEGORI</t>
   </si>
   <si>
@@ -133,16 +141,23 @@
   </si>
   <si>
     <t>OTHER CATEGORIES</t>
+  </si>
+  <si>
+    <t>HARGA BELI</t>
+  </si>
+  <si>
+    <t>HARGA JUAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-[$Rp-3809]* #,##0.00_-;\-[$Rp-3809]* #,##0.00_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +183,13 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -222,25 +244,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Accent6" xfId="1" builtinId="49"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -561,8 +588,8 @@
     <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="26" style="9" customWidth="1"/>
     <col min="8" max="8" width="38.140625" customWidth="1"/>
     <col min="9" max="9" width="23.140625" customWidth="1"/>
     <col min="10" max="10" width="21.85546875" customWidth="1"/>
@@ -572,179 +599,179 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2"/>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3"/>
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3"/>
-      <c r="F3" s="3"/>
-      <c r="H3" s="5" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4"/>
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4"/>
-      <c r="F4" s="3"/>
-      <c r="H4" s="5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H5" s="5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H6" s="5" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H7" s="5" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H8" s="5" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H9" s="5" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H10" s="5" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H11" s="5" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H12" s="5" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H13" s="5" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H14" s="5" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H15" s="5" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H16" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H16" s="5" t="s">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="5" t="s">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H18" s="5" t="s">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H19" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H19" s="5" t="s">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H20" s="5" t="s">
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="5" t="s">
+    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H22" s="5" t="s">
+    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H23" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H23" s="5" t="s">
+    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H24" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H24" s="5" t="s">
+    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H25" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H25" s="5" t="s">
+    <row r="26" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H26" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H26" s="5" t="s">
+    <row r="27" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H27" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H27" s="5" t="s">
+    <row r="28" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H28" s="5" t="s">
+    <row r="29" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H29" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H30" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H30" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
